--- a/OLD/reverse_Nostoc_sp_P0A4U6.xlsx
+++ b/OLD/reverse_Nostoc_sp_P0A4U6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -466,27 +476,583 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[(11, 2), (12, 1), (13, 0)]</t>
+          <t>[(8, 5), (9, 4), (10, 3), (11, 2), (12, 1), (13, 0)]</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.649382099447238</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GTATCATATGATAC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GTATCA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TGATAC</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TA&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0001999200319872051</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[(5, 4), (6, 3), (7, 2), (8, 1)]</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3198962193550263</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TATCATAT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TATC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ATAT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[(4, 3), (5, 2), (6, 1)]</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>4.15851133962548</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GTA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TAC</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0004</v>
+      <c r="D4" t="n">
+        <v>0.3317506651167402</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TATCAT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TAT</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[(5, 3), (6, 2), (7, 1)]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3309660851704451</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TATCATA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TAT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;C&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[(7, 3), (8, 2), (9, 1)]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5057817253733858</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TATCATATG</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TAT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;CAT&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[(10, 6), (11, 5), (12, 4)]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5499322143373919</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CATATGATA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;ATG&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[(10, 7), (11, 6), (12, 5)]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.292812540001719</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ATATGATA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TG&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[(10, 8), (11, 7), (12, 6)]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.330998366598219</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TATGATA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TAT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;G&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[(10, 9), (11, 8), (12, 7)]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2892065711458709</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ATGATA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[(3, 1), (4, 0)]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.639457038196664</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GTATC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9990003998400639</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[(4, 2), (5, 1)]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4686423651105062</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TATCA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[(10, 2), (11, 1)]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2099445137771713</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TATCATATGAT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;TCATATG&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[(11, 3), (12, 2)]</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3444059593677849</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ATCATATGATA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;CATATGA&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[(11, 9), (12, 8)]</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4588186356213609</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TGATA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;A&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9998000799680128</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[(12, 10), (13, 9)]</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4906159758665896</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GATAC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9998000799680128</v>
       </c>
     </row>
   </sheetData>

--- a/OLD/reverse_Nostoc_sp_P0A4U6.xlsx
+++ b/OLD/reverse_Nostoc_sp_P0A4U6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.0001999200319872051</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -586,6 +601,11 @@
       <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -664,6 +689,11 @@
       <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -703,6 +733,11 @@
       <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -742,6 +777,11 @@
       <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -781,6 +821,11 @@
       <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -820,6 +865,11 @@
       <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -859,6 +909,11 @@
       <c r="I11" t="n">
         <v>0.9990003998400639</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -898,6 +953,11 @@
       <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -937,6 +997,11 @@
       <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -976,6 +1041,11 @@
       <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1015,6 +1085,11 @@
       <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1053,6 +1128,11 @@
       </c>
       <c r="I16" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ambiguous IR</t>
+        </is>
       </c>
     </row>
   </sheetData>
